--- a/data_generation/10_aquatic_toxicity/fludioxonil_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/fludioxonil_aquatic_toxicity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60042EE-8968-4443-A1BD-E9F4530A6A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23366C62-1F72-4342-927B-D71BC7CC11E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="1560" windowWidth="28785" windowHeight="8790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aquatic toxicity" sheetId="1" r:id="rId1"/>
@@ -195,9 +195,6 @@
     <t>In the EFSA conclusion, the effect is erroneously specified as "mortality". Corrected based on the dRAR</t>
   </si>
   <si>
-    <t>ini</t>
-  </si>
-  <si>
     <t>shell growth</t>
   </si>
   <si>
@@ -226,6 +223,9 @@
   </si>
   <si>
     <t>j.efsa.2024.9047_LoEP</t>
+  </si>
+  <si>
+    <t>im</t>
   </si>
 </sst>
 </file>
@@ -570,30 +570,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.7265625" customWidth="1"/>
-    <col min="3" max="3" width="31.7265625" customWidth="1"/>
-    <col min="4" max="4" width="7.7265625" customWidth="1"/>
-    <col min="5" max="6" width="11.7265625" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" customWidth="1"/>
-    <col min="9" max="9" width="12.7265625" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" customWidth="1"/>
-    <col min="11" max="11" width="5.7265625" customWidth="1"/>
-    <col min="12" max="12" width="4.7265625" customWidth="1"/>
-    <col min="13" max="13" width="6.7265625" customWidth="1"/>
-    <col min="14" max="14" width="4.7265625" customWidth="1"/>
-    <col min="15" max="15" width="8.7265625" customWidth="1"/>
-    <col min="16" max="16" width="16.7265625" customWidth="1"/>
-    <col min="17" max="17" width="4.7265625" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" customWidth="1"/>
-    <col min="19" max="19" width="9.7265625" customWidth="1"/>
-    <col min="20" max="20" width="4.7265625" customWidth="1"/>
-    <col min="21" max="21" width="8.7265625" customWidth="1"/>
+    <col min="1" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="5" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" customWidth="1"/>
+    <col min="14" max="14" width="4.7109375" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="20" max="20" width="4.7109375" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +610,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -696,7 +696,7 @@
         <v>46</v>
       </c>
       <c r="P2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q2">
         <v>63</v>
@@ -714,7 +714,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -749,7 +749,7 @@
         <v>46</v>
       </c>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q3">
         <v>63</v>
@@ -767,7 +767,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -802,7 +802,7 @@
         <v>46</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q4">
         <v>63</v>
@@ -820,7 +820,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -855,7 +855,7 @@
         <v>46</v>
       </c>
       <c r="P5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q5">
         <v>63</v>
@@ -873,7 +873,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -908,7 +908,7 @@
         <v>46</v>
       </c>
       <c r="P6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q6">
         <v>63</v>
@@ -926,7 +926,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -961,7 +961,7 @@
         <v>46</v>
       </c>
       <c r="P7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q7">
         <v>63</v>
@@ -979,7 +979,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>46</v>
       </c>
       <c r="P8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q8">
         <v>63</v>
@@ -1032,7 +1032,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>46</v>
       </c>
       <c r="P9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q9">
         <v>63</v>
@@ -1082,7 +1082,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>43</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
         <v>31</v>
@@ -1114,7 +1114,7 @@
         <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q10">
         <v>63</v>
@@ -1132,7 +1132,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
         <v>32</v>
@@ -1164,7 +1164,7 @@
         <v>46</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q11">
         <v>63</v>
@@ -1182,7 +1182,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K12" t="s">
         <v>31</v>
@@ -1214,7 +1214,7 @@
         <v>46</v>
       </c>
       <c r="P12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q12">
         <v>63</v>
@@ -1232,7 +1232,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>43</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K13" t="s">
         <v>31</v>
@@ -1264,7 +1264,7 @@
         <v>51</v>
       </c>
       <c r="P13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q13">
         <v>63</v>
@@ -1282,7 +1282,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K14" t="s">
         <v>31</v>
@@ -1314,7 +1314,7 @@
         <v>46</v>
       </c>
       <c r="P14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q14">
         <v>63</v>
@@ -1332,7 +1332,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>43</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K15" t="s">
         <v>31</v>
@@ -1364,7 +1364,7 @@
         <v>46</v>
       </c>
       <c r="P15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q15">
         <v>63</v>
@@ -1382,7 +1382,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>46</v>
       </c>
       <c r="P16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q16">
         <v>64</v>
@@ -1438,7 +1438,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>46</v>
       </c>
       <c r="P17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q17">
         <v>64</v>
@@ -1494,7 +1494,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>46</v>
       </c>
       <c r="P18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q18">
         <v>64</v>
@@ -1547,7 +1547,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1582,10 +1582,10 @@
         <v>25</v>
       </c>
       <c r="O19" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="P19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q19">
         <v>64</v>
@@ -1603,7 +1603,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>50</v>
       </c>
       <c r="J20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K20" t="s">
         <v>34</v>
@@ -1638,7 +1638,7 @@
         <v>46</v>
       </c>
       <c r="P20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q20">
         <v>64</v>
@@ -1656,7 +1656,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1670,10 +1670,10 @@
         <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K21" t="s">
         <v>31</v>
@@ -1691,7 +1691,7 @@
         <v>46</v>
       </c>
       <c r="P21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q21">
         <v>64</v>
@@ -1709,7 +1709,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1723,10 +1723,10 @@
         <v>43</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K22" t="s">
         <v>31</v>
@@ -1744,7 +1744,7 @@
         <v>46</v>
       </c>
       <c r="P22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q22">
         <v>64</v>
@@ -1762,7 +1762,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1776,10 +1776,10 @@
         <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K23" t="s">
         <v>31</v>
@@ -1797,7 +1797,7 @@
         <v>46</v>
       </c>
       <c r="P23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q23">
         <v>64</v>
@@ -1815,7 +1815,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>44</v>
       </c>
       <c r="I24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K24" t="s">
         <v>34</v>
@@ -1850,7 +1850,7 @@
         <v>46</v>
       </c>
       <c r="P24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q24">
         <v>64</v>
@@ -1868,7 +1868,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1882,10 +1882,10 @@
         <v>48</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K25" t="s">
         <v>34</v>
@@ -1903,7 +1903,7 @@
         <v>46</v>
       </c>
       <c r="P25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q25">
         <v>64</v>
@@ -1921,7 +1921,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -1935,10 +1935,10 @@
         <v>48</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K26" t="s">
         <v>32</v>
@@ -1956,7 +1956,7 @@
         <v>46</v>
       </c>
       <c r="P26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q26">
         <v>64</v>
@@ -1974,7 +1974,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -1988,10 +1988,10 @@
         <v>48</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K27" t="s">
         <v>34</v>
@@ -2009,7 +2009,7 @@
         <v>46</v>
       </c>
       <c r="P27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q27">
         <v>64</v>
@@ -2027,7 +2027,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2041,10 +2041,10 @@
         <v>48</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K28" t="s">
         <v>31</v>
@@ -2062,7 +2062,7 @@
         <v>46</v>
       </c>
       <c r="P28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q28">
         <v>64</v>
@@ -2080,7 +2080,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2094,10 +2094,10 @@
         <v>48</v>
       </c>
       <c r="G29" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" t="s">
         <v>60</v>
-      </c>
-      <c r="I29" t="s">
-        <v>61</v>
       </c>
       <c r="K29" t="s">
         <v>34</v>
@@ -2115,7 +2115,7 @@
         <v>46</v>
       </c>
       <c r="P29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q29">
         <v>64</v>
@@ -2133,7 +2133,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2150,10 +2150,10 @@
         <v>48</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K30" t="s">
         <v>34</v>
@@ -2171,7 +2171,7 @@
         <v>51</v>
       </c>
       <c r="P30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q30">
         <v>64</v>
@@ -2189,7 +2189,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2206,10 +2206,10 @@
         <v>48</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K31" t="s">
         <v>32</v>
@@ -2227,7 +2227,7 @@
         <v>51</v>
       </c>
       <c r="P31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q31">
         <v>64</v>
@@ -2245,7 +2245,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2262,10 +2262,10 @@
         <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K32" t="s">
         <v>34</v>
@@ -2283,7 +2283,7 @@
         <v>51</v>
       </c>
       <c r="P32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q32">
         <v>64</v>
